--- a/attendance_history/absent_2026-03-29.xlsx
+++ b/attendance_history/absent_2026-03-29.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,60 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>mwesigwa rebecca</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-24140</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>AJUNA WILLFRED</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-22274</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>BIT</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SOMAC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
